--- a/gex_pivot_levels_2026-10-16.xlsx
+++ b/gex_pivot_levels_2026-10-16.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,12 +544,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>-$22.65M</t>
+          <t>-$29.32M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$44.07M</t>
+          <t>+$51.14M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>-$72.76M</t>
+          <t>-$76.12M</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>+$119.46M</t>
+          <t>+$118.16M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -593,124 +593,116 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>7746.15</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>766</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="n">
+        <v>7760.19</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>-$30.19M</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>+$141.74M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>7766.22</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>768</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>+$4.16M</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>+$51.90M</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>7760.19</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-$45.30M</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+$126.30M</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>7785.19</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>-$31.16M</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>+$152.25M</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>7766.22</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>768</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>-$55.29M</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>+$111.41M</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>+$564.70K</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+$94.21M</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7785.19</v>
+        <v>7786.29</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7725</v>
+        <v>770</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+$690.46K</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-$16.66M</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>+$90.84M</t>
+          <t>+$251.42M</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -722,10 +714,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7786.29</v>
+        <v>7796.32</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -734,74 +726,78 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-$32.53M</t>
+          <t>-$1.83M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$262.53M</t>
+          <t>+$134.36M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>7796.32</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="n">
+        <v>7806.36</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>772</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>+$4.68M</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>+$102.33M</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>-$177.89M</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>+$331.31M</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>7806.36</v>
+        <v>7810.19</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>772</v>
+        <v>7750</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>-$241.38M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>+$41.93M</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>+$342.04M</t>
+          <t>+$666.86M</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -811,49 +807,49 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>7820.19</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>7760</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>+$6.12M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$41.91M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>7810.19</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>7750</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>+$39.41M</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>+$622.04M</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7820.19</v>
+        <v>7835.19</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7760</v>
+        <v>7775</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
@@ -862,82 +858,82 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>+$5.80M</t>
+          <t>+$9.88M</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>+$39.90M</t>
+          <t>+$143.71M</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>7835.19</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>7775</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="n">
+        <v>7836.46</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>775</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>+$121.99M</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>+$228.10M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7850.19</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7790</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>+$9.73M</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>+$143.06M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>7836.46</v>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>775</v>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>+$103.03M</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>+$219.00M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>+$32.66M</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+$45.55M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -945,10 +941,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7850.19</v>
+        <v>7855.19</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>7790</v>
+        <v>7795</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -957,12 +953,12 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>+$33.98M</t>
+          <t>+$15.36M</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>+$47.38M</t>
+          <t>+$23.60M</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -972,63 +968,63 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>7860.19</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7800</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>+$30.72M</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>+$225.02M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
           <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7855.19</v>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>7795</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$16.25M</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>+$24.89M</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7856.53</v>
+        <v>7865.19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>777</v>
+        <v>7805</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>+$1.64M</t>
+          <t>+$11.06M</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>+$70.01M</t>
+          <t>+$22.24M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1043,33 +1039,33 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>7860.19</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="n">
+        <v>7870.19</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7810</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>+$33.13M</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>+$244.01M</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+$50.53M</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>+$60.86M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -1077,134 +1073,35 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7865.19</v>
+        <v>7936.8</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>7805</v>
+        <v>785</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>+$11.85M</t>
+          <t>+$31.95M</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>+$23.96M</t>
+          <t>+$32.09M</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>7870.19</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>7810</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>+$54.98M</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>+$66.55M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>7886.63</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>+$56.05M</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>+$84.58M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>7936.8</v>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>785</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+$34.07M</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>+$34.34M</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2360,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2410,33 +2307,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
-        <v>2766.5</v>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>2736.32</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>-$274.35M</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>+$353.99M</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>-$126.22M</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+$149.23M</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -2444,35 +2341,167 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
+        <v>2756.44</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>-$76.71M</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+$163.88M</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>2766.5</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>-$176.87M</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>+$367.56M</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
         <v>2786.62</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B5" s="2" t="n">
         <v>277</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>IWM</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>-$76.74M</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>+$188.69M</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-$55.61M</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+$200.02M</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2796.68</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-$652.12K</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>+$116.68M</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2806.74</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>-$42.91M</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+$87.71M</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3702,7 +3731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3776,12 +3805,12 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>+$39.41M</t>
+          <t>+$41.93M</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>+$622.04M</t>
+          <t>+$666.86M</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -3814,12 +3843,12 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>-$274.35M</t>
+          <t>-$176.87M</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>+$353.99M</t>
+          <t>+$367.56M</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -3852,12 +3881,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>-$241.38M</t>
+          <t>-$177.89M</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>+$342.04M</t>
+          <t>+$331.31M</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -3890,12 +3919,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>-$32.53M</t>
+          <t>-$16.66M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>+$262.53M</t>
+          <t>+$251.42M</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3912,24 +3941,24 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>7860.19</v>
+        <v>7836.46</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7800</v>
+        <v>775</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>+$33.13M</t>
+          <t>+$121.99M</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>+$244.01M</t>
+          <t>+$228.10M</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -3950,24 +3979,24 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7836.46</v>
+        <v>7860.19</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>775</v>
+        <v>7800</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>+$103.03M</t>
+          <t>+$30.72M</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>+$219.00M</t>
+          <t>+$225.02M</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -4000,12 +4029,12 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>-$76.74M</t>
+          <t>-$55.61M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>+$188.69M</t>
+          <t>+$200.02M</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -4016,68 +4045,68 @@
       <c r="H8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>30284.74</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>730</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>-$5.62M</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>+$154.35M</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2756.44</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>-$76.71M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>+$163.88M</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>7760.19</v>
+        <v>30284.74</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>7700</v>
+        <v>730</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>-$31.16M</t>
+          <t>-$5.62M</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>+$152.25M</t>
+          <t>+$154.35M</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -4094,172 +4123,176 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2736.32</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>-$126.22M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>+$149.23M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>7835.19</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C12" s="2" t="n">
         <v>7775</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>+$9.73M</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>+$143.06M</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>+$9.88M</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>+$143.71M</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>7736.12</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>765</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="B13" s="5" t="n">
+        <v>7760.19</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-$30.19M</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>+$141.74M</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7796.32</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>-$72.76M</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>+$119.46M</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>30079.14</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>725</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>-$27.31M</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>+$114.09M</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>7766.22</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>768</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>-$55.29M</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>+$111.41M</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>-$1.83M</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>+$134.36M</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>29873.54</v>
+        <v>7766.22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>-$21.78M</t>
+          <t>-$45.30M</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>+$106.14M</t>
+          <t>+$126.30M</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4270,76 +4303,80 @@
       <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>7796.32</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="B16" s="5" t="n">
+        <v>7736.12</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>765</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>+$4.68M</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>+$102.33M</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>-$76.12M</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>+$118.16M</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7785.19</v>
+        <v>2796.68</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7725</v>
+        <v>278</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>+$690.46K</t>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-$652.12K</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>+$90.84M</t>
+          <t>+$116.68M</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4348,24 +4385,24 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>30202.5</v>
+        <v>30079.14</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>+$1.68M</t>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>-$27.31M</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>+$85.17M</t>
+          <t>+$114.09M</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -4376,114 +4413,106 @@
       <c r="H18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>30449.22</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>734</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="n">
+        <v>29873.54</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>-$18.92M</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>+$84.80M</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-$21.78M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>+$106.14M</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>7886.63</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>780</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>+$56.05M</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>+$84.58M</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="n">
+        <v>7785.19</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>+$564.70K</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>+$94.21M</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>29996.9</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>723</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>-$63.18M</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>+$79.56M</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2806.74</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>-$42.91M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$87.71M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -4492,76 +4521,72 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7856.53</v>
+        <v>30202.5</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>777</v>
+        <v>728</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>+$1.64M</t>
+          <t>+$1.68M</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>+$70.01M</t>
+          <t>+$85.17M</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>30449.22</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>734</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>-$18.92M</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>+$84.80M</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>7870.19</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>7810</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>+$54.98M</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>+$66.55M</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4572,24 +4597,24 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>30695.94</v>
+        <v>29996.9</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>+$27.81M</t>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>-$63.18M</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>+$62.45M</t>
+          <t>+$79.56M</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -4599,35 +4624,35 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>4174.63</v>
+        <v>30695.94</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>380</v>
+        <v>740</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>-$4.98M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>+$27.81M</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>+$52.34M</t>
+          <t>+$62.45M</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -4637,7 +4662,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4648,24 +4673,24 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7746.15</v>
+        <v>7870.19</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>766</v>
+        <v>7810</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>+$4.16M</t>
+          <t>+$50.53M</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>+$51.90M</t>
+          <t>+$60.86M</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -4680,40 +4705,40 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>30243.62</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>729</v>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>+$10.97M</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>+$49.39M</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4174.63</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>380</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>-$4.98M</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>+$52.34M</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -4724,36 +4749,32 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7850.19</v>
+        <v>7685.95</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7790</v>
+        <v>760</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>+$33.98M</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>-$29.32M</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>+$47.38M</t>
+          <t>+$51.14M</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -4762,24 +4783,24 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>30161.38</v>
+        <v>30243.62</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-$14.53M</t>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>+$10.97M</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>+$46.70M</t>
+          <t>+$49.39M</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -4789,77 +4810,85 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7685.95</v>
+        <v>30161.38</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>-$22.65M</t>
+          <t>-$14.53M</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>+$44.07M</t>
+          <t>+$46.70M</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>29667.94</v>
+        <v>7850.19</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>715</v>
+        <v>7790</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>-$22.86M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>+$32.66M</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>+$41.43M</t>
+          <t>+$45.55M</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -4880,12 +4909,12 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>+$5.80M</t>
+          <t>+$6.12M</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>+$39.90M</t>
+          <t>+$41.91M</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4906,10 +4935,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>29791.3</v>
+        <v>29667.94</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -4918,24 +4947,20 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>-$4.29M</t>
+          <t>-$22.86M</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>+$38.18M</t>
+          <t>+$41.43M</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -4944,10 +4969,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>29750.18</v>
+        <v>29791.3</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -4956,12 +4981,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>-$28.64M</t>
+          <t>-$4.29M</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>+$37.07M</t>
+          <t>+$38.18M</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4971,43 +4996,47 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7936.8</v>
+        <v>29750.18</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>785</v>
+        <v>717</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>+$34.07M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>-$28.64M</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>+$34.34M</t>
+          <t>+$37.07M</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5050,40 +5079,36 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>30120.26</v>
+        <v>7936.8</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>726</v>
+        <v>785</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>-$447.94K</t>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>+$31.95M</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>+$29.79M</t>
+          <t>+$32.09M</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -5092,10 +5117,10 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>29544.57</v>
+        <v>30120.26</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -5104,46 +5129,50 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>-$12.58M</t>
+          <t>-$447.94K</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>+$28.05M</t>
+          <t>+$29.79M</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>4284.49</v>
+        <v>29544.57</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>390</v>
+        <v>712</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>+$1.78M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>-$12.58M</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>+$25.30M</t>
+          <t>+$28.05M</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5156,28 +5185,28 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>29462.33</v>
+        <v>4284.49</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>710</v>
+        <v>390</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>-$17.92M</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>+$1.78M</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>+$25.04M</t>
+          <t>+$25.30M</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5190,40 +5219,36 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>7855.19</v>
+        <v>29462.33</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>7795</v>
+        <v>710</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>+$16.25M</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>-$17.92M</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>+$24.89M</t>
+          <t>+$25.04M</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -5270,70 +5295,70 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
+        <v>7855.19</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>7795</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>+$15.36M</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>+$23.60M</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>7865.19</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C44" s="2" t="n">
         <v>7805</v>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>+$11.85M</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>+$23.96M</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>29256.73</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>705</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>-$17.44M</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>+$20.80M</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>+$11.06M</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>+$22.24M</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
@@ -5342,28 +5367,28 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>4155.12</v>
+        <v>29256.73</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>86</v>
+        <v>705</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>-$9.17M</t>
+          <t>-$17.44M</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>+$16.15M</t>
+          <t>+$20.80M</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -5384,10 +5409,10 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>4348.38</v>
+        <v>4155.12</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
@@ -5396,12 +5421,12 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>-$115.20K</t>
+          <t>-$9.17M</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>+$15.48M</t>
+          <t>+$16.15M</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -5418,28 +5443,28 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>95.72</v>
+        <v>4348.38</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>+$9.75M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>-$115.20K</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>+$12.95M</t>
+          <t>+$15.48M</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -5449,35 +5474,35 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>4275.91</v>
+        <v>95.72</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>88.5</v>
+        <v>155</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>+$10.42M</t>
+          <t>+$9.75M</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>+$12.05M</t>
+          <t>+$12.95M</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -5494,74 +5519,74 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4275.91</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>+$10.42M</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>+$12.05M</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B50" s="5" t="n">
         <v>98.81</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>+$7.12M</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>+$8.72M</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>4240.54</v>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>386</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>+$3.65M</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>+$7.62M</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5574,70 +5599,70 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
+        <v>4240.54</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>+$3.65M</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>+$7.62M</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
         <v>4372.54</v>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C52" s="2" t="n">
         <v>90.5</v>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>GDX</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>+$7.15M</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>+$7.19M</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>4394.35</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>400</v>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>+$2.78M</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>+$7.01M</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5650,70 +5675,74 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
+        <v>4394.35</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>+$2.78M</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>+$7.01M</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
         <v>4119.7</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="5" t="n">
         <v>375</v>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>-$4.05M</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>+$6.30M</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G54" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>4203.43</v>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>-$2.39M</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>+$5.29M</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -5722,70 +5751,66 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
+        <v>4203.43</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>-$2.39M</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>+$5.29M</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
         <v>4295.47</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C56" s="2" t="n">
         <v>391</v>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>+$4.75M</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>+$5.17M</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>92.64</v>
-      </c>
-      <c r="C56" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>+$1.64M</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>+$5.12M</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -5794,28 +5819,28 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>4064.77</v>
+        <v>92.64</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>-$2.28M</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>+$1.64M</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>+$5.09M</t>
+          <t>+$5.12M</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -5825,35 +5850,35 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>30266.9</v>
+        <v>4064.77</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>30000</v>
+        <v>370</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>+$973.51K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>-$2.28M</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>+$4.72M</t>
+          <t>+$5.09M</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
@@ -5863,157 +5888,157 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>30266.9</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>+$973.51K</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>+$4.72M</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B60" s="5" t="n">
         <v>96.95999999999999</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="5" t="n">
         <v>157</v>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>+$3.83M</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>+$4.51M</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B61" s="2" t="n">
         <v>4218.57</v>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C61" s="2" t="n">
         <v>384</v>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>+$2.81M</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>+$4.41M</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B62" s="5" t="n">
         <v>4339.42</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="5" t="n">
         <v>395</v>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>+$2.64M</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>+$4.35M</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>29380.09</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>708</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>-$2.10M</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>+$3.66M</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -6022,28 +6047,28 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>4251.53</v>
+        <v>29380.09</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>387</v>
+        <v>708</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>+$129.38K</t>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>-$2.10M</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>+$3.26M</t>
+          <t>+$3.66M</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6053,81 +6078,81 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>97.58</v>
+        <v>4251.53</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>158</v>
+        <v>387</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>+$723.50K</t>
+          <t>+$129.38K</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>+$3.02M</t>
+          <t>+$3.26M</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>4262.52</v>
+        <v>97.58</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>388</v>
+        <v>158</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>+$2.18M</t>
+          <t>+$723.50K</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>+$2.98M</t>
+          <t>+$3.02M</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -6136,104 +6161,108 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>4420.85</v>
+        <v>4262.52</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>91.5</v>
+        <v>388</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>+$2.73M</t>
+          <t>+$2.18M</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>+$2.75M</t>
+          <t>+$2.98M</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>96.34</v>
+        <v>4420.85</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>156</v>
+        <v>91.5</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>+$1.41M</t>
+          <t>+$2.73M</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>+$2.31M</t>
+          <t>+$2.75M</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>4010.17</v>
+        <v>96.34</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>-$1.93M</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>+$1.41M</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>+$2.24M</t>
+          <t>+$2.31M</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -6242,142 +6271,138 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>4141.67</v>
+        <v>4010.17</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>+$811.35K</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>-$1.93M</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>+$2.18M</t>
+          <t>+$2.24M</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>101.9</v>
+        <v>4141.67</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>165</v>
+        <v>377</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>+$1.36M</t>
+          <t>+$811.35K</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>+$1.51M</t>
+          <t>+$2.18M</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>+$1.36M</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>+$1.51M</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B71" s="2" t="n">
+      <c r="B72" s="2" t="n">
         <v>30216.9</v>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C72" s="2" t="n">
         <v>29950</v>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>-$62.27K</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>+$1.32M</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>30366.9</v>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>30100</v>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>+$1.03M</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>+$1.26M</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -6386,96 +6411,100 @@
         </is>
       </c>
       <c r="B73" s="5" t="n">
+        <v>30366.9</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>30100</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>+$1.03M</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>+$1.26M</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
         <v>30166.9</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>29900</v>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>-$538.84K</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>+$1.15M</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n">
-        <v>89.55</v>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>-$326.83K</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>+$1.13M</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>30241.9</v>
+        <v>89.55</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>29975</v>
+        <v>145</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>+$26.34K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>-$326.83K</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>+$1.10M</t>
+          <t>+$1.13M</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -6488,218 +6517,214 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>30241.9</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>29975</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>+$26.34K</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>+$1.10M</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n">
+      <c r="B77" s="2" t="n">
         <v>4273.5</v>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C77" s="2" t="n">
         <v>389</v>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>+$461.36K</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>+$1.09M</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B78" s="5" t="n">
         <v>30066.9</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>29800</v>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>-$271.82K</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>+$754.38K</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n">
+      <c r="B79" s="2" t="n">
         <v>97.27</v>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C79" s="2" t="n">
         <v>157.5</v>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>USO</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>+$616.99K</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>+$660.71K</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B80" s="5" t="n">
         <v>30191.9</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C80" s="5" t="n">
         <v>29925</v>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D80" s="6" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>-$465.80K</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>+$654.99K</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="n">
-        <v>4086.74</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>372</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>-$560.48K</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>+$646.01K</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>94.18000000000001</v>
+        <v>4086.74</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>152.5</v>
+        <v>372</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>+$63.54K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>-$560.48K</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>+$587.75K</t>
+          <t>+$646.01K</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6709,43 +6734,47 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>30116.9</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>29850</v>
+        <v>152.5</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>-$169.73K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>+$63.54K</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>+$463.70K</t>
+          <t>+$587.75K</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -6754,62 +6783,58 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>30291.9</v>
+        <v>30116.9</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>30025</v>
+        <v>29850</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>+$222.72K</t>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>-$169.73K</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>+$405.93K</t>
+          <t>+$463.70K</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>4372.37</v>
+        <v>30291.9</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>398</v>
+        <v>30025</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>+$338.62K</t>
+          <t>+$222.72K</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>+$393.27K</t>
+          <t>+$405.93K</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6819,43 +6844,47 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>30316.9</v>
+        <v>4372.37</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>30050</v>
+        <v>398</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>+$161.95K</t>
+          <t>+$338.62K</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>+$379.28K</t>
+          <t>+$393.27K</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -6864,10 +6893,10 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>30226.9</v>
+        <v>30316.9</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>29960</v>
+        <v>30050</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -6876,50 +6905,46 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>+$319.71K</t>
+          <t>+$161.95K</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>+$362.82K</t>
+          <t>+$379.28K</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>4328.43</v>
+        <v>30226.9</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>394</v>
+        <v>29960</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>+$156.37K</t>
+          <t>+$319.71K</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>+$272.27K</t>
+          <t>+$362.82K</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6929,35 +6954,35 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>30286.9</v>
+        <v>4328.43</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>30020</v>
+        <v>394</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>-$21.55K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>+$156.37K</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>+$129.32K</t>
+          <t>+$272.27K</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6978,24 +7003,24 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>30086.9</v>
+        <v>30286.9</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>29820</v>
+        <v>30020</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>+$72.44K</t>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>-$21.55K</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>+$92.20K</t>
+          <t>+$129.32K</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -7005,7 +7030,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -7016,10 +7041,10 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>30186.9</v>
+        <v>30086.9</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>29920</v>
+        <v>29820</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -7028,12 +7053,12 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>+$39.51K</t>
+          <t>+$72.44K</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>+$89.81K</t>
+          <t>+$92.20K</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -7054,24 +7079,24 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>30296.9</v>
+        <v>30186.9</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>30030</v>
+        <v>29920</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>-$17.96K</t>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>+$39.51K</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>+$75.44K</t>
+          <t>+$89.81K</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -7081,7 +7106,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -7092,39 +7117,77 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
+        <v>30296.9</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>30030</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>-$17.96K</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>+$75.44K</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
         <v>30236.9</v>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C93" s="2" t="n">
         <v>29970</v>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>-$7.18K</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>+$43.11K</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H92"/>
+  <autoFilter ref="A1:H93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>